--- a/templates/oncall-import-template.xlsx
+++ b/templates/oncall-import-template.xlsx
@@ -127,7 +127,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -142,7 +142,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -157,7 +157,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -172,7 +172,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -187,7 +187,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -202,7 +202,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -217,7 +217,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -232,7 +232,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -247,7 +247,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -262,7 +262,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -356,7 +356,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -376,7 +376,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -406,7 +406,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -421,7 +421,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -436,7 +436,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
